--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:04</t>
+    <t xml:space="preserve">2026-09-29 18:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,7 +521,7 @@
         <v>3.05</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35.35</v>
+        <v>35.34</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>32.3</v>
@@ -535,7 +535,7 @@
         <v>-1.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46.89</v>
+        <v>46.88</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>48.38</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:37</t>
+    <t xml:space="preserve">2026-10-05 04:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,7 +521,7 @@
         <v>3.05</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35.34</v>
+        <v>35.35</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>32.3</v>
@@ -535,10 +535,10 @@
         <v>-1.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46.88</v>
+        <v>46.89</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>48.38</v>
+        <v>48.39</v>
       </c>
     </row>
   </sheetData>
